--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETENTOR BENGALA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETENTOR BENGALA.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RETENTOR BENG IRON TITAN150-160/ FAN125-150 2009/ FAN160/ BROS XNR125-150-160/ XRE190/ PCX150/ CBX200 041632</t>
+          <t>RETENTOR BENGALA  IRON TITAN150-160/ FAN125-150 2009/ FAN160/ BROS XNR125-150-160/ XRE190/ PCX150/ CBX200 041632</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -470,7 +470,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RETENTOR BENG IRON SUSUKI YES125/ KATANA 176231</t>
+          <t>RETENTOR BENGALA  IRON SUSUKI YES125/ KATANA 176231</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RETENTOR BENG TRILHA FAN TITAN150 2004 A 2015/ TITAN FAN160 2016 A 2021/ XRE190 2016 A 2021/ PCX150 2014 A 2018/ CBX200</t>
+          <t>RETENTOR BENGALA  TRILHA FAN TITAN150 2004 A 2015/ TITAN FAN160 2016 A 2021/ XRE190 2016 A 2021/ PCX150 2014 A 2018/ CBX200</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RETENTOR BENG TRILHA YBR125/ FACTOR125-150</t>
+          <t>RETENTOR BENGALA  TRILHA YBR125/ FACTOR125-150</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RETENTOR BENG TRILHA SHINERAY XY 50Q</t>
+          <t>RETENTOR BENGALA  TRILHA SHINERAY XY 50Q</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RETENTOR BENG IRON CROSSER XTZ150 2014 A 2021</t>
+          <t>RETENTOR BENGALA  IRON CROSSER XTZ150 2014 A 2021</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RETENTOR BENG IRON CG TITAN 2000 KS/ FAN125/ BIZ125 041629</t>
+          <t>RETENTOR BENGALA  IRON CG TITAN 2000 KS/ FAN125/ BIZ125 041629</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RETENTOR BENG MOTOPORT YBR125 1210747</t>
+          <t>RETENTOR BENGALA  MOTOPORT YBR125 1210747</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RETENTOR BENG TRILHA FAZER250 2018</t>
+          <t>RETENTOR BENGALA  TRILHA FAZER250 2018</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RETENTOR BENG MOTOPORT CG TITAN FAN 1101753</t>
+          <t>RETENTOR BENGALA  MOTOPORT CG TITAN FAN 1101753</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RETENTOR BENG SMARTFOX CROSSER XTZ150 2014</t>
+          <t>RETENTOR BENGALA  SMARTFOX CROSSER XTZ150 2014</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RETENTOR BENG PCX150 2014 A 2018</t>
+          <t>RETENTOR BENGALA  PCX150 2014 A 2018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RETENTOR BENG MOTOPORT FAZER250 2018</t>
+          <t>RETENTOR BENGALA  MOTOPORT FAZER250 2018</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RETENTOR BENG IRON YBR/ KATANA 041630</t>
+          <t>RETENTOR BENGALA  IRON YBR/ KATANA 041630</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RETENTOR BENG C/ GUARDA PÓ UNIK FAN CG TITAN150-160</t>
+          <t>RETENTOR BENGALA  C/ GUARDA PÓ UNIK FAN CG TITAN150-160</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RETENTOR BENG MOTOPORT XT660 1211217</t>
+          <t>RETENTOR BENGALA  MOTOPORT XT660 1211217</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RETENTOR BENG VEDAMOTORS CROSSER XTZ150 2014/ XV250 VIRAGO 1988 A 1997 </t>
+          <t xml:space="preserve">RETENTOR BENGALA  VEDAMOTORS CROSSER XTZ150 2014/ XV250 VIRAGO 1988 A 1997 </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RETENTOR BENG VEDAMOTORS FAZER250 2012/ ZX600-750-1100</t>
+          <t>RETENTOR BENGALA  VEDAMOTORS FAZER250 2012/ ZX600-750-1100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RETENTOR BENG TRILHA FAZER250 2012 A 2017/ GS500</t>
+          <t>RETENTOR BENGALA  TRILHA FAZER250 2012 A 2017/ GS500</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RETENTOR BENG MOTOPORT LANDER XTZ250 1210277</t>
+          <t>RETENTOR BENGALA  MOTOPORT LANDER XTZ250 1210277</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RETENTOR BENG TRILHA TORNADO XR250/ TWISTER CBX250/ CB500 2005/ FAZER250/ CB250 TWISTER 2019 A 2022</t>
+          <t>RETENTOR BENGALA  TRILHA TORNADO XR250/ TWISTER CBX250/ CB500 2005/ FAZER250/ CB250 TWISTER 2019 A 2022</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RETENTOR BENG SMARTFOX CG TITAN FAN BIZ POP</t>
+          <t>RETENTOR BENGALA  SMARTFOX CG TITAN FAN BIZ POP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RETENTOR BENG IRON CB300/ CB500/ CBX250 TWISTER/ FAZER250 176227</t>
+          <t>RETENTOR BENGALA  IRON CB300/ CB500/ CBX250 TWISTER/ FAZER250 176227</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RETENTOR BENG MOTOPORT CG TITAN 1101777</t>
+          <t>RETENTOR BENGALA  MOTOPORT CG TITAN 1101777</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RETENTOR BENG MOTOPORT NXR150 1102380</t>
+          <t>RETENTOR BENGALA  MOTOPORT NXR150 1102380</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RETENTOR BENG MOTOPORT CBX250 NXR/ XR200 1102379</t>
+          <t>RETENTOR BENGALA  MOTOPORT CBX250 NXR/ XR200 1102379</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RETENTOR BENG IRON BIZ125 185508</t>
+          <t>RETENTOR BENGALA  IRON BIZ125 185508</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RETENTOR BENG TRILHA TORNADO250 2001 A 2008/ FALCON400 1999 A 2008/ LANDER250 2007 A 2014/ XRE300 2009 A 2020 </t>
+          <t xml:space="preserve">RETENTOR BENGALA  TRILHA TORNADO250 2001 A 2008/ FALCON400 1999 A 2008/ LANDER250 2007 A 2014/ XRE300 2009 A 2020 </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RETENTOR BENG IRON CBX250 NX/ XR200 187607</t>
+          <t>RETENTOR BENGALA  IRON CBX250 NX/ XR200 187607</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RETENTOR BENG IRON TITAN150-160/ CG FAN125 2009/ BRS NXR125-150-160/ XRE190/ CBX200 STRADA 176236</t>
+          <t>RETENTOR BENGALA  IRON TITAN150-160/ CG FAN125 2009/ BRS NXR125-150-160/ XRE190/ CBX200 STRADA 176236</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RETENTOR BENG RENTEC (PAR) TWISTER/ CB500</t>
+          <t>RETENTOR BENGALA  RENTEC (PAR) TWISTER/ CB500</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RETENTOR BENG (PAR) PEÇA+ XR250 TORNADO/ XRE300/ LANDER XTZ250/ HORNET/ CB500/ FALCON</t>
+          <t>RETENTOR BENGALA  (PAR) PEÇA+ XR250 TORNADO/ XRE300/ LANDER XTZ250/ HORNET/ CB500/ FALCON</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RETENTOR BENG RENTEC (PAR) CG125/ BIZ100-125/ PO100</t>
+          <t>RETENTOR BENGALA  RENTEC (PAR) CG125/ BIZ100-125/ PO100</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">RETENTOR BENG BHD INTRUDER125/ YES125 SUSUKI </t>
+          <t xml:space="preserve">RETENTOR BENGALA  BHD INTRUDER125/ YES125 SUSUKI </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RETENTOR BENG DEMTEC TWISTER</t>
+          <t>RETENTOR BENGALA  DEMTEC TWISTER</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RETENTOR BENG EXTREMO CB300/ TWISTER250</t>
+          <t>RETENTOR BENGALA  EXTREMO CB300/ TWISTER250</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RETENTOR BENG EMBUS NX200/ XTZ125/ DT180</t>
+          <t>RETENTOR BENGALA  EMBUS NX200/ XTZ125/ DT180</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RETENTOR BENG GRAPKS XR200/ TWISTER CBX250/ CB300</t>
+          <t>RETENTOR BENGALA  GRAPKS XR200/ TWISTER CBX250/ CB300</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETENTOR BENGALA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETENTOR BENGALA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>32</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,7 +492,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,7 +512,6 @@
           <t>22</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +532,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -562,7 +552,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -583,7 +572,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -604,7 +592,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -625,7 +612,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -646,7 +632,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -667,7 +652,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -688,7 +672,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -709,7 +692,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -730,7 +712,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -751,7 +732,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -772,7 +752,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -793,7 +772,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -814,7 +792,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -835,7 +812,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -856,7 +832,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -877,7 +852,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -898,7 +872,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -919,7 +892,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -940,7 +912,6 @@
           <t>19</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -961,7 +932,6 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -982,7 +952,6 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1003,7 +972,6 @@
           <t>29</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1024,7 +992,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1045,7 +1012,6 @@
           <t>39</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1066,7 +1032,6 @@
           <t>32</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1087,7 +1052,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1108,7 +1072,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1129,7 +1092,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1150,7 +1112,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1171,7 +1132,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1192,11 +1152,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1217,7 +1172,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1238,7 +1192,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
